--- a/claude-with-tools/plots/c++_tool_types.xlsx
+++ b/claude-with-tools/plots/c++_tool_types.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emmayu/Desktop/llm-with-tools/claude-with-tools/plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F78B945E-9556-BF40-A2C4-F2AC0068F425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5765A13-D7C6-0145-AE24-318624C0F9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" activeTab="4" xr2:uid="{E2D6E1E7-5E36-D543-A33D-4921A5871149}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="10">
   <si>
     <t>model name</t>
   </si>
@@ -60,16 +60,16 @@
     <t>read</t>
   </si>
   <si>
-    <t>git show</t>
-  </si>
-  <si>
-    <t>git log</t>
-  </si>
-  <si>
     <t>ls</t>
   </si>
   <si>
     <t>edit</t>
+  </si>
+  <si>
+    <t>git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">git </t>
   </si>
 </sst>
 </file>
@@ -465,10 +465,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BE515AD-2E43-A447-AB98-93F98F5642FD}">
-  <dimension ref="A3:H5"/>
+  <dimension ref="A3:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -482,19 +482,16 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="29">
+    </row>
+    <row r="4" spans="1:7" ht="29">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -508,19 +505,16 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="29">
+    </row>
+    <row r="5" spans="1:7" ht="29">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -540,9 +534,6 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
         <v>0</v>
       </c>
     </row>
@@ -553,10 +544,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73905DFF-74A8-8645-87B0-D4651908EC73}">
-  <dimension ref="A3:H5"/>
+  <dimension ref="A3:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -570,19 +561,16 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="29">
+    </row>
+    <row r="4" spans="1:7" ht="29">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -599,16 +587,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="29">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -628,9 +613,6 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
         <v>0</v>
       </c>
     </row>
@@ -641,10 +623,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CBC3C83-7735-6947-8D5E-160E006C6143}">
-  <dimension ref="A3:H5"/>
+  <dimension ref="A3:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -658,19 +640,16 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="29">
+    </row>
+    <row r="4" spans="1:7" ht="29">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -692,11 +671,8 @@
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="29">
+    </row>
+    <row r="5" spans="1:7" ht="29">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -716,9 +692,6 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
         <v>0</v>
       </c>
     </row>
@@ -729,10 +702,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835E2CA7-5526-6545-9E8C-78FBF2384BE2}">
-  <dimension ref="A3:H5"/>
+  <dimension ref="A3:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -746,19 +719,16 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="29">
+    </row>
+    <row r="4" spans="1:7" ht="29">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -780,11 +750,8 @@
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="29">
+    </row>
+    <row r="5" spans="1:7" ht="29">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -804,9 +771,6 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
         <v>0</v>
       </c>
     </row>
@@ -817,10 +781,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9D8F76-F7F2-4E48-96A8-8EF84545DAD6}">
-  <dimension ref="A3:H5"/>
+  <dimension ref="A3:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -834,19 +798,16 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="29">
+    </row>
+    <row r="4" spans="1:7" ht="29">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -866,13 +827,10 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="29">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -892,9 +850,6 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
         <v>0</v>
       </c>
     </row>
